--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.25158800019744</v>
+        <v>1.665883050032084</v>
       </c>
       <c r="D2" t="n">
-        <v>9.24725254248056</v>
+        <v>1.502678538153091</v>
       </c>
       <c r="E2" t="n">
-        <v>15.2657818480713</v>
+        <v>2.480689550311586</v>
       </c>
       <c r="F2" t="n">
-        <v>15.84218544975403</v>
+        <v>2.57435513558503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.78315169634003</v>
+        <v>6.627262150655256</v>
       </c>
       <c r="D3" t="n">
-        <v>40.93162344198862</v>
+        <v>6.651388809323151</v>
       </c>
       <c r="E3" t="n">
-        <v>15.2657818480713</v>
+        <v>2.480689550311586</v>
       </c>
       <c r="F3" t="n">
-        <v>15.84218544975403</v>
+        <v>2.57435513558503</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
